--- a/docs/enterprise-context/synthetic/apexretail/05-vendors-contract-inventory.xlsx
+++ b/docs/enterprise-context/synthetic/apexretail/05-vendors-contract-inventory.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="276">
   <si>
     <t>Dataset</t>
   </si>
@@ -504,6 +504,111 @@
     <t>CON-VEN-GENESYS</t>
   </si>
   <si>
+    <t>VEN-RELEX</t>
+  </si>
+  <si>
+    <t>RELEX Solutions</t>
+  </si>
+  <si>
+    <t>CON-RELEX-2026</t>
+  </si>
+  <si>
+    <t>RELEX Solutions Enterprise Services Agreement</t>
+  </si>
+  <si>
+    <t>Retail Planning Analytics</t>
+  </si>
+  <si>
+    <t>Finance Technology</t>
+  </si>
+  <si>
+    <t>2024-10-01</t>
+  </si>
+  <si>
+    <t>2027-10-28</t>
+  </si>
+  <si>
+    <t>CON-VEN-RELEX</t>
+  </si>
+  <si>
+    <t>VEN-SNOW</t>
+  </si>
+  <si>
+    <t>CON-SNOW-2026</t>
+  </si>
+  <si>
+    <t>ServiceNow Enterprise Services Agreement</t>
+  </si>
+  <si>
+    <t>ITSM / CMDB</t>
+  </si>
+  <si>
+    <t>2024-11-01</t>
+  </si>
+  <si>
+    <t>2027-11-28</t>
+  </si>
+  <si>
+    <t>CON-VEN-SNOW</t>
+  </si>
+  <si>
+    <t>VEN-MICROSOFT</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>CON-MICROSOFT-2026</t>
+  </si>
+  <si>
+    <t>Microsoft Enterprise Services Agreement</t>
+  </si>
+  <si>
+    <t>Productivity and Cloud</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2027-12-28</t>
+  </si>
+  <si>
+    <t>CON-VEN-MICROSOFT</t>
+  </si>
+  <si>
+    <t>VEN-AWS</t>
+  </si>
+  <si>
+    <t>Amazon Web Services</t>
+  </si>
+  <si>
+    <t>CON-AWS-2026</t>
+  </si>
+  <si>
+    <t>Amazon Web Services Enterprise Services Agreement</t>
+  </si>
+  <si>
+    <t>Cloud Hosting</t>
+  </si>
+  <si>
+    <t>CON-VEN-AWS</t>
+  </si>
+  <si>
+    <t>VEN-AZURE</t>
+  </si>
+  <si>
+    <t>Microsoft Azure</t>
+  </si>
+  <si>
+    <t>CON-AZURE-2026</t>
+  </si>
+  <si>
+    <t>Microsoft Azure Enterprise Services Agreement</t>
+  </si>
+  <si>
+    <t>CON-VEN-AZURE</t>
+  </si>
+  <si>
     <t>VEN-DATABRICKS</t>
   </si>
   <si>
@@ -516,100 +621,10 @@
     <t>Databricks Enterprise Services Agreement</t>
   </si>
   <si>
-    <t>Retail Analytics</t>
-  </si>
-  <si>
-    <t>Finance Technology</t>
-  </si>
-  <si>
-    <t>2024-10-01</t>
-  </si>
-  <si>
-    <t>2027-10-28</t>
+    <t>Data Platform</t>
   </si>
   <si>
     <t>CON-VEN-DATABRICKS</t>
-  </si>
-  <si>
-    <t>VEN-SNOW</t>
-  </si>
-  <si>
-    <t>CON-SNOW-2026</t>
-  </si>
-  <si>
-    <t>ServiceNow Enterprise Services Agreement</t>
-  </si>
-  <si>
-    <t>ITSM / CMDB</t>
-  </si>
-  <si>
-    <t>2024-11-01</t>
-  </si>
-  <si>
-    <t>2027-11-28</t>
-  </si>
-  <si>
-    <t>CON-VEN-SNOW</t>
-  </si>
-  <si>
-    <t>VEN-MICROSOFT</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>CON-MICROSOFT-2026</t>
-  </si>
-  <si>
-    <t>Microsoft Enterprise Services Agreement</t>
-  </si>
-  <si>
-    <t>Productivity and Cloud</t>
-  </si>
-  <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2027-12-28</t>
-  </si>
-  <si>
-    <t>CON-VEN-MICROSOFT</t>
-  </si>
-  <si>
-    <t>VEN-AWS</t>
-  </si>
-  <si>
-    <t>Amazon Web Services</t>
-  </si>
-  <si>
-    <t>CON-AWS-2026</t>
-  </si>
-  <si>
-    <t>Amazon Web Services Enterprise Services Agreement</t>
-  </si>
-  <si>
-    <t>Cloud Hosting</t>
-  </si>
-  <si>
-    <t>CON-VEN-AWS</t>
-  </si>
-  <si>
-    <t>VEN-AZURE</t>
-  </si>
-  <si>
-    <t>Microsoft Azure</t>
-  </si>
-  <si>
-    <t>CON-AZURE-2026</t>
-  </si>
-  <si>
-    <t>Microsoft Azure Enterprise Services Agreement</t>
-  </si>
-  <si>
-    <t>CON-VEN-AZURE</t>
-  </si>
-  <si>
-    <t>Data Platform</t>
   </si>
   <si>
     <t>VEN-SNOWFLAKE</t>
@@ -2591,19 +2606,19 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="E16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F16" t="s">
         <v>35</v>
@@ -2633,7 +2648,7 @@
         <v>90</v>
       </c>
       <c r="O16" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="P16" t="s">
         <v>35</v>
@@ -2653,19 +2668,19 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D17" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E17" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F17" t="s">
         <v>35</v>
@@ -2695,7 +2710,7 @@
         <v>90</v>
       </c>
       <c r="O17" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="P17" t="s">
         <v>35</v>
@@ -2715,19 +2730,19 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D18" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F18" t="s">
         <v>35</v>
@@ -2757,7 +2772,7 @@
         <v>90</v>
       </c>
       <c r="O18" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="P18" t="s">
         <v>35</v>
@@ -2777,19 +2792,19 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C19" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F19" t="s">
         <v>35</v>
@@ -2819,7 +2834,7 @@
         <v>90</v>
       </c>
       <c r="O19" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="P19" t="s">
         <v>35</v>
@@ -2839,19 +2854,19 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E20" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F20" t="s">
         <v>35</v>
@@ -2881,7 +2896,7 @@
         <v>90</v>
       </c>
       <c r="O20" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="P20" t="s">
         <v>35</v>
@@ -2901,19 +2916,19 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D21" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E21" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F21" t="s">
         <v>35</v>
@@ -2943,7 +2958,7 @@
         <v>90</v>
       </c>
       <c r="O21" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="P21" t="s">
         <v>35</v>
@@ -2963,19 +2978,19 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C22" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D22" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E22" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F22" t="s">
         <v>35</v>
@@ -3005,7 +3020,7 @@
         <v>90</v>
       </c>
       <c r="O22" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="P22" t="s">
         <v>35</v>
@@ -3025,19 +3040,19 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C23" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D23" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F23" t="s">
         <v>35</v>
@@ -3067,7 +3082,7 @@
         <v>90</v>
       </c>
       <c r="O23" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="P23" t="s">
         <v>35</v>
@@ -3087,19 +3102,19 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C24" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D24" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E24" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F24" t="s">
         <v>35</v>
@@ -3129,7 +3144,7 @@
         <v>90</v>
       </c>
       <c r="O24" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="P24" t="s">
         <v>35</v>
@@ -3149,19 +3164,19 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C25" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D25" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E25" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F25" t="s">
         <v>35</v>
@@ -3191,7 +3206,7 @@
         <v>90</v>
       </c>
       <c r="O25" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s">
         <v>35</v>
@@ -3211,19 +3226,19 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D26" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E26" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F26" t="s">
         <v>35</v>
@@ -3253,7 +3268,7 @@
         <v>90</v>
       </c>
       <c r="O26" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="P26" t="s">
         <v>35</v>
@@ -3273,19 +3288,19 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E27" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F27" t="s">
         <v>35</v>
@@ -3315,7 +3330,7 @@
         <v>90</v>
       </c>
       <c r="O27" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="P27" t="s">
         <v>35</v>
@@ -3335,19 +3350,19 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C28" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D28" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E28" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F28" t="s">
         <v>35</v>
@@ -3377,7 +3392,7 @@
         <v>90</v>
       </c>
       <c r="O28" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="P28" t="s">
         <v>35</v>
